--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -2221,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2600,76 +2600,78 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>&lt;100&gt; amplitude</t>
+          <t>Di-interstitial binding</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A_100</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
+          <t>E_b_i2</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>eV</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DISABLED pending a two-parameter (A_111,B_111) refit -- blank = use A_111/A_100 verbatim. Setting this alone rescales the ENTIRE small-n branch by E_b_i2*2^-B_111/A_111 and suppresses loop nucleation; see docs/design_notes/validation_10dpa_revision3.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>&lt;100&gt; exponent</t>
+          <t>&lt;100&gt; amplitude</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B_100</t>
+          <t>A_100</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3581</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>eV</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Blend center</t>
+          <t>&lt;100&gt; exponent</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>n_tr</t>
+          <t>B_100</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>0.3581</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SIAs</t>
+          <t>−</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Blend width</t>
+          <t>Blend center</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sigma_tr</t>
+          <t>n_tr</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2680,109 +2682,104 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>He Maximum Loading</t>
+          <t>Blend width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sigma_tr</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SIAs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>He/V ratio parameter</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>alpha_He</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>l_max = alpha * m^(2/3)</t>
+          <t>He Maximum Loading</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>He Binding Energy to Bubbles (Eqs. 76-77)</t>
+          <t>He/V ratio parameter</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>alpha_He</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>l_max = alpha * m^(2/3)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>He atomic mass</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>m_He</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4.0026</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>amu</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>4-He</t>
+          <t>He Binding Energy to Bubbles (Eqs. 76-77)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>He virial B2</t>
+          <t>He atomic mass</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>m_He</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.67e-29</v>
+        <v>4.0026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>m^3/atom</t>
+          <t>amu</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Table 8</t>
+          <t>4-He</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>He virial B3</t>
+          <t>He virial B2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.84e-58</v>
+        <v>1.67e-29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>m^6/atom^2</t>
+          <t>m^3/atom</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2794,73 +2791,73 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>He Binding: Atomistic-Continuum Blending (Table 19)</t>
+          <t>He virial B3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.84e-58</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>m^6/atom^2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Table 8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Decay constant</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>mu_He</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>He^-1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ln(100)/7</t>
+          <t>He Binding: Atomistic-Continuum Blending (Table 19)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fitting amplitude A^He(2)</t>
+          <t>Decay constant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A_He_2</t>
+          <t>mu_He</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.55</v>
+        <v>0.658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>eV</t>
+          <t>He^-1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caturla/Fu</t>
+          <t>ln(100)/7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fitting amplitude A^He(3)</t>
+          <t>Fitting amplitude A^He(2)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A_He_3</t>
+          <t>A_He_2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2876,16 +2873,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fitting amplitude A^He(4)</t>
+          <t>Fitting amplitude A^He(3)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A_He_4</t>
+          <t>A_He_3</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2901,68 +2898,68 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Trap Mutation (Eq. 83, Eq. 142, Table 27)</t>
+          <t>Fitting amplitude A^He(4)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A_He_4</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Caturla/Fu</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attempt frequency</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>nu0_TM</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1000000000000</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>s^-1</t>
+          <t>Trap Mutation (Eq. 83, Eq. 142, Table 27)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>E_TM: He5V1</t>
+          <t>Attempt frequency</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>E_TM_1_5</t>
+          <t>nu0_TM</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>1000000000000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>eV</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Morishita 2003</t>
+          <t>s^-1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E_TM: He6V1</t>
+          <t>E_TM: He5V1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E_TM_1_6</t>
+          <t>E_TM_1_5</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2978,16 +2975,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>E_TM: He7V1</t>
+          <t>E_TM: He6V1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E_TM_1_7</t>
+          <t>E_TM_1_6</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2996,23 +2993,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>spontaneous</t>
+          <t>Morishita 2003</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E_TM: He4 (alpha=0)</t>
+          <t>E_TM: He7V1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>E_TM_0_4</t>
+          <t>E_TM_1_7</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3021,23 +3018,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gao 2011</t>
+          <t>spontaneous</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E_TM: He5 (alpha=0)</t>
+          <t>E_TM: He4 (alpha=0)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>E_TM_0_5</t>
+          <t>E_TM_0_4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3053,23 +3050,48 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>E_TM: He5 (alpha=0)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>E_TM_0_5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Gao 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>E_TM: He6 (alpha=0)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>E_TM_0_6</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C44" t="n">
         <v>0</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>eV</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>spontaneous</t>
         </is>
@@ -3086,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -4090,6 +4112,182 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Loop -&gt; Network Dislocation Loss (loop_network_loss.tex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Channel enable flag</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LOOP_NETWORK_LOSS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0=off (legacy 2_0 behaviour), 1=on; requires sim.run_adaptive()</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Elastic capture range</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>loop_net_chi</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>R_int = chi*d_loop; CHANNEL IS ~0 BELOW chi~30 (few-nm loops vs ~100 nm network spacing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Capture width</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>loop_net_w_c</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>blank = per-character Burgers vector (physical); 150*b_111 reaches the EUROFER plateau</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Recovery prefactor</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>loop_net_K_rec</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>drho = -K_rec*rho_net^{3/2}; 0 = no recovery (monotonic growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Network density ceiling</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>loop_net_rho_max</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1e+16</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>m^-2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>runaway guard; EUROFER experimental plateau is ~5e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Small-n stress floor</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>loop_net_xi</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>elastic-zone floor for small n; 0 = off</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Incorporation onset size</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>loop_net_n_inc</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>blank = i_mobile; loops below this size are excluded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3333,39 +3333,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Vacancy bias factor</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Loop interstitial bias</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Z_v</t>
+          <t>Z_i_loop</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Table 26</t>
+          <t>Eq. P3_i; LOOP bias, independent of Z_i (network). Shipped = current effective value so behaviour is unchanged; physical range 1.05-1.30. Blank = use Z_i.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>He bias factor</t>
+          <t>Vacancy bias factor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Z_He</t>
+          <t>Z_v</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3385,121 +3385,126 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Grain Boundary Sink (Eq. 134-137)</t>
+          <t>He bias factor</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Z_He</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Table 26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grain diameter</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>d_g</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>EUROFER typical</t>
+          <t>Grain Boundary Sink (Eq. 134-137)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Precipitate Sink (Eq. 134-137)</t>
+          <t>Grain diameter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>d_g</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EUROFER typical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Precipitate density</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>rho_p</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1e+20</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>m^-3</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M23C6 precipitates</t>
+          <t>Precipitate Sink (Eq. 134-137)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Precipitate radius</t>
+          <t>Precipitate density</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>r_p</t>
+          <t>rho_p</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5e-08</v>
+        <v>1e+20</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m^-3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EUROFER typical</t>
+          <t>M23C6 precipitates</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Precipitate bias SIA</t>
+          <t>Precipitate radius</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Z_p_i</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
+          <t>r_p</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>5e-08</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EUROFER typical</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Precipitate bias vac</t>
+          <t>Precipitate bias SIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Z_p_v</t>
+          <t>Z_p_i</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3514,43 +3519,43 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Radiation Re-solution (Eq. 143)</t>
+          <t>Precipitate bias vac</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Z_p_v</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>−</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Re-solution parameter (fission)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>b0_fission</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>dpa^-1/He</t>
+          <t>Radiation Re-solution (Eq. 143)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Re-solution parameter (fusion)</t>
+          <t>Re-solution parameter (fission)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>b0_fusion</t>
+          <t>b0_fission</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3561,98 +3566,93 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>He State-Space Parameters (Table 29)</t>
+          <t>Re-solution parameter (fusion)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>b0_fusion</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dpa^-1/He</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>He max loading parameter</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>alpha_He</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>−</t>
+          <t>He State-Space Parameters (Table 29)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Max He per cluster</t>
+          <t>He max loading parameter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L_He_max</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>mf</t>
-        </is>
+          <t>alpha_He</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>−</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>mf=mean-field</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Size-Bin Moment Parameters (Chapter 9)</t>
+          <t>Max He per cluster</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>L_He_max</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mf</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>mf=mean-field</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Bin ratio</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>r_ratio</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Eq. 188</t>
+          <t>Size-Bin Moment Parameters (Chapter 9)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Moments per bin</t>
+          <t>Bin ratio</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>n_moments</t>
+          <t>r_ratio</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3665,23 +3665,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>zeroth + first</t>
+          <t>Eq. 188</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Min cluster size n1</t>
+          <t>Moments per bin</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>n1_bin</t>
+          <t>n_moments</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3690,23 +3690,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eq. 188</t>
+          <t>zeroth + first</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Grouping transition</t>
+          <t>Min cluster size n1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>n_group</t>
+          <t>n1_bin</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,166 +3715,166 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eq. 190</t>
+          <t>Eq. 188</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Solver Settings (Table 29)</t>
+          <t>Grouping transition</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>n_group</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Eq. 190</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Irradiation Conditions</t>
+          <t>Solver Settings (Table 29)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>573</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>irradiation temperature</t>
+          <t>Irradiation Conditions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Displacement rate</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>1e-06</v>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>573</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>dpa/s</t>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>irradiation temperature</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>He production rate</t>
+          <t>Displacement rate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>G_He_r</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1e-06</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>appm/dpa</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>for fusion use ~10</t>
+          <t>dpa/s</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>He production rate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>G_He_r</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>appm/dpa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>for fusion use ~10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>Neutron spectrum</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>spectrum</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>fission</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>fission | fusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Loop 1/2&lt;111&gt; -&gt; &lt;100&gt; Conversion (Marian 2002 + Dudarev 2008)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unary barrier offset</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>E_a0_conv</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>eV</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Dudarev unary E_a^0; Marian dH2 ~ 1.0 eV</t>
+          <t>Loop 1/2&lt;111&gt; -&gt; &lt;100&gt; Conversion (Marian 2002 + Dudarev 2008)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unary barrier size slope</t>
+          <t>Unary barrier offset</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gamma_a_conv</t>
+          <t>E_a0_conv</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.03</v>
+        <v>1.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3883,98 +3883,98 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>per perimeter-segment; calibrate to Arakawa onset</t>
+          <t>Dudarev unary E_a^0; Marian dH2 ~ 1.0 eV</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unary attempt frequency</t>
+          <t>Unary barrier size slope</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nu0_conv</t>
+          <t>gamma_a_conv</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10000000000000</v>
+        <v>0.03</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1/s</t>
+          <t>eV</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Debye</t>
+          <t>per perimeter-segment; calibrate to Arakawa onset</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Conversion crossover temp</t>
+          <t>Unary attempt frequency</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T_star_conv_C</t>
+          <t>nu0_conv</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>450</v>
+        <v>10000000000000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1/s</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>dF(n_ref,T*)=0; in [350,550] (Dudarev Fig.4)</t>
+          <t>Debye</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Conversion reference size</t>
+          <t>Conversion crossover temp</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>n_ref_conv</t>
+          <t>T_star_conv_C</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>calibration anchor size for LoopEnergetics</t>
+          <t>dF(n_ref,T*)=0; in [350,550] (Dudarev Fig.4)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junction peak yield</t>
+          <t>Conversion reference size</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>phi_max_junc</t>
+          <t>n_ref_conv</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3983,23 +3983,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marian; yield at n=n_prime (0-1)</t>
+          <t>calibration anchor size for LoopEnergetics</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junction log-size tol.</t>
+          <t>Junction peak yield</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sigma_s_junc</t>
+          <t>phi_max_junc</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4008,23 +4008,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marian comparable-size width in ln(n/np)</t>
+          <t>Marian; yield at n=n_prime (0-1)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Junction min size</t>
+          <t>Junction log-size tol.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>n_j_min_junc</t>
+          <t>sigma_s_junc</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>0.35</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4033,23 +4033,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marian; junctions from n ~ 34-37</t>
+          <t>Marian comparable-size width in ln(n/np)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>&lt;100&gt; loop-onset size</t>
+          <t>Junction min size</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>n_loop_min</t>
+          <t>n_j_min_junc</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4058,32 +4058,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>bulk-100 n_min; below this no &lt;100&gt; loop</t>
+          <t>Marian; junctions from n ~ 34-37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Two-step barrier</t>
+          <t>&lt;100&gt; loop-onset size</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>dH2_conv</t>
+          <t>n_loop_min</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>eV</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;&lt;100&gt; fwd</t>
+          <t>bulk-100 n_min; below this no &lt;100&gt; loop</t>
         </is>
       </c>
     </row>
@@ -4095,11 +4095,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dH_rev_conv</t>
+          <t>dH2_conv</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4108,55 +4108,55 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;1/2&lt;111&gt; rev</t>
+          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;&lt;100&gt; fwd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Loop -&gt; Network Dislocation Loss (loop_network_loss.tex)</t>
+          <t>Two-step barrier</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dH_rev_conv</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;1/2&lt;111&gt; rev</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Channel enable flag</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>LOOP_NETWORK_LOSS</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0=off (legacy 2_0 behaviour), 1=on; requires sim.run_adaptive()</t>
+          <t>Loop -&gt; Network Dislocation Loss (loop_network_loss.tex)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Elastic capture range</t>
+          <t>Channel enable flag</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>loop_net_chi</t>
+          <t>LOOP_NETWORK_LOSS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4165,124 +4165,149 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>R_int = chi*d_loop; CHANNEL IS ~0 BELOW chi~30 (few-nm loops vs ~100 nm network spacing)</t>
+          <t>0=off (legacy 2_0 behaviour), 1=on; requires sim.run_adaptive()</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Capture width</t>
+          <t>Elastic capture range</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>loop_net_w_c</t>
-        </is>
+          <t>loop_net_chi</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>blank = per-character Burgers vector (physical); 150*b_111 reaches the EUROFER plateau</t>
+          <t>R_int = chi*d_loop; CHANNEL IS ~0 BELOW chi~30 (few-nm loops vs ~100 nm network spacing)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Recovery prefactor</t>
+          <t>Capture width</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>loop_net_K_rec</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
+          <t>loop_net_w_c</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>drho = -K_rec*rho_net^{3/2}; 0 = no recovery (monotonic growth)</t>
+          <t>blank = per-character Burgers vector (physical); 150*b_111 reaches the EUROFER plateau</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Network density ceiling</t>
+          <t>Recovery prefactor</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>loop_net_rho_max</t>
+          <t>loop_net_K_rec</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1e+16</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>m^-2</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>runaway guard; EUROFER experimental plateau is ~5e14</t>
+          <t>drho = -K_rec*rho_net^{3/2}; 0 = no recovery (monotonic growth)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Small-n stress floor</t>
+          <t>Network density ceiling</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>loop_net_xi</t>
+          <t>loop_net_rho_max</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1e+16</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m^-2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>elastic-zone floor for small n; 0 = off</t>
+          <t>runaway guard; EUROFER experimental plateau is ~5e14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Small-n stress floor</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>loop_net_xi</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>elastic-zone floor for small n; 0 = off</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Incorporation onset size</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>loop_net_n_inc</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>blank = i_mobile; loops below this size are excluded</t>
         </is>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -4313,6 +4313,31 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Junction min-size fraction</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>n_j_min_frac</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>n_j_min_eff = min(n_j_min_junc, ceil(frac*i_mobile)); 0.6 keeps 30 at i_mobile=50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -4338,6 +4338,31 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>&lt;100&gt; absorption boost</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>absorb_boost_100</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Scales K_100_absorb only (1D-glide enhanced capture). 1.0 = legacy; rot_factor ~ 6568 is the upper bound</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -4363,6 +4363,53 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>&lt;100&gt; absorption barrier</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dH2_abs_conv</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Forward barrier for the ABSORPTION success gate P_succ^abs = A_abs*[1+exp((dH2_abs-dH_rev)/kT)]^-1. Blank = dH2_conv (legacy, coupled to junction). Usable 0.30-0.70; junction is 1.00. A &lt;=i_mobile cluster joining a large &lt;100&gt; loop is templated by the host and should not pay the junction reversion penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>&lt;100&gt; absorption prefactor</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>psucc_abs_pref</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>A_abs in P_succ^abs; caps the gate at A_abs/2, so gate&gt;0.5 needs A_abs&gt;1. 1.0 = legacy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10000000000000</v>
+        <v>100000000000000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EUROFER tempered</t>
+          <t>EUROFER97 normalised+tempered martensite. Cold-worked / heavily tempered lath martensite runs 5e14-1e15 m^-2. [2026-08-16: was 1e+13, too low for a tempered-martensitic steel]</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.001</v>
+        <v>4e-07</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EUROFER typical</t>
+          <t>EUROFER97 martensite LATH width 0.3-0.5 um.  Was 1e-3 m (1 mm), which gave k2_gb = pi^2/d_g^2 = 9.9e6 m^-2, seven orders below the dislocation sink -- the GB channel was off in all but name.  pi^2/d_g^2 is the lowest slab eigenmode, so lath WIDTH is the right length here.  [2026-08-16: was 0.001]</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1e+20</v>
+        <v>1e+21</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>M23C6 precipitates</t>
+          <t>Effective single population standing in for M23C6 (~1e20 m^-3, r~50 nm) + MX V/Ta carbonitrides (~1e21 m^-3, r~15 nm).  Chosen with r_p=2e-8 to reproduce the COMBINED k2_p = 4*pi*r*rho ~ 2.5e14 m^-2.  [2026-08-16: was 1e+20]</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5e-08</v>
+        <v>2e-08</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EUROFER typical</t>
+          <t>Effective radius of the combined M23C6+MX population; see rho_p.  [2026-08-16: was 5e-08]</t>
         </is>
       </c>
     </row>
@@ -4407,6 +4407,56 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>A_abs in P_succ^abs; caps the gate at A_abs/2, so gate&gt;0.5 needs A_abs&gt;1. 1.0 = legacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Lath boundary bias SIA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Z_gb_i</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Boundary sink bias for SIAs. 1.0 = unbiased = legacy behaviour. Added 2026-08-16: the boundary sink was identical for both species, so it could carry no net bias -- harmless at d_g=1 mm, first-order at the lath width.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lath boundary bias vac</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Z_gb_v</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Boundary sink bias for vacancies; paired with Z_gb_i. He is deliberately left unbiased.</t>
         </is>
       </c>
     </row>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="16820" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Production" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Energetics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Diffusion" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dissociation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reactions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energetics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diffusion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dissociation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reactions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0.2487192267849093</v>
       </c>
       <c r="D3" t="n">
-        <v>0.28</v>
+        <v>0.2487192267849093</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.05</v>
+        <v>0.317274</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>0.317274</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>2.5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>2.217946866693871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.34</v>
+        <v>0.4018086195196494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.06</v>
+        <v>0.07350444561211728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.3</v>
+        <v>2.213153281253307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="37.6640625" customWidth="1" min="1" max="1"/>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.34</v>
+        <v>0.4018086195196494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.06</v>
+        <v>0.07350444561211728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>1016.124131086688</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2207,6 +2207,31 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>Eq. 128</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Max mobile SIA cluster size</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>i_mobile</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Calibration row 8700. Read from the Diffusion sheet by _calculate_derived (d = self.diffusion); default is 1.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2318,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>2.217946866693871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2313,7 +2338,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.22</v>
+        <v>0.2129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2338,7 +2363,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5756</v>
+        <v>0.7157090107816463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2522,7 +2547,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.22</v>
+        <v>0.2129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2614,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.3873</v>
+        <v>0.3136878686724647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,6 +2632,9 @@
         <is>
           <t>E_b_i2</t>
         </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.75</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3319,7 +3347,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3344,7 +3372,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>1.181300416775048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3426,7 +3454,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4e-07</v>
+        <v>1e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3458,7 +3486,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1e+21</v>
+        <v>1e+20</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3508,7 +3536,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3528,7 +3556,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3874,7 +3902,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3974,7 +4002,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3999,7 +4027,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4099,7 +4127,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0.4394554538170355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4181,7 +4209,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4205,6 +4233,9 @@
           <t>loop_net_w_c</t>
         </is>
       </c>
+      <c r="C53" t="n">
+        <v>2.482e-08</v>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>m</t>
@@ -4228,7 +4259,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4374,6 +4405,9 @@
           <t>dH2_abs_conv</t>
         </is>
       </c>
+      <c r="C60" t="n">
+        <v>0.36</v>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>eV</t>
@@ -4422,7 +4456,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4447,16 +4481,148 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Boundary sink bias for vacancies; paired with Z_gb_i. He is deliberately left unbiased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Loop coalescence and size-dependent bias (calibration 8700)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOOP COAL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LOOP_COAL</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>1</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Boundary sink bias for vacancies; paired with Z_gb_i. He is deliberately left unbiased.</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1 = enable loop-loop coalescence (glide capture). Calibration row 8700.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>loop coal pref</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>loop_coal_pref</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>30</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Prefactor on the loop-loop encounter rate. Calibration row 8700.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Z loop model</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Z_loop_model</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0 = constant Z_i_loop (legacy); 1 = Wolfer size-dependent loop bias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>r cap i b</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>r_cap_i_b</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SIA capture radius at the loop core, in units of b_111 (Wolfer model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>r cap v b</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>r_cap_v_b</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Vacancy capture radius at the loop core, in units of b_111 (Wolfer model).</t>
         </is>
       </c>
     </row>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>573</v>
+        <v>603.15</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>irradiation temperature</t>
+          <t>Condition S330 (330 C), the BOR-60 EUROFER97 point row 8700 was fitted to.</t>
         </is>
       </c>
     </row>
@@ -3823,11 +3823,16 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1e-06</v>
+        <v>1e-07</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>dpa/s</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EXPERIMENTAL rate. 1e-6 was the accelerated screening rate used in S1-S7.</t>
         </is>
       </c>
     </row>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.09</v>
+        <v>0.1240170802921057</v>
       </c>
       <c r="D7" t="n">
         <v>0.09</v>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.317274</v>
+        <v>0.55</v>
       </c>
       <c r="D12" t="n">
         <v>0.317274</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.217946866693871</v>
+        <v>2.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.217946866693871</v>
+        <v>2.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>100000000000000</v>
+        <v>500000000000000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.482e-08</v>
+        <v>1.241e-09</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1e+16</v>
+        <v>500000000000000</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4628,6 +4628,26 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>Vacancy capture radius at the loop core, in units of b_111 (Wolfer model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>&lt;100&gt; growth boost</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>grow_boost_100</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>campaign fixed block (run_ensemble); added 2026-09-04</t>
         </is>
       </c>
     </row>

--- a/RadCluster_2_1/input/input_parameters.xlsx
+++ b/RadCluster_2_1/input/input_parameters.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="D12" t="n">
         <v>0.317274</v>
@@ -3136,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -4651,6 +4651,100 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cavity network sweeping on</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>VOID_NETWORK_LOSS</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Cavity -&gt; network-dislocation sweeping. 0 = off (legacy, byte-identical). A moving line that intersects a cavity absorbs it whole; the m vacancies go to J_VAC_fixed. Only cavity sink that does not act through c_v, so it does not disturb the loop drive. Added 2026-09-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sweep capture-width factor</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>void_net_chi</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>w_c = chi * d_cav. NOT an elastic radius at this magnitude: chi~1e3 means the swept volume is ~1000x what network CLIMB supplies (climb moves a line 1.9 um over 40 dpa), so chi is a GLIDE-rate proxy absorbing the mobile-dislocation velocity. Calibrated with f_cl_v=0.65 -&gt; 6/6 at 15 dpa; the two are COUPLED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sweep onset size</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>void_net_m_inc</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sizes 1..m_inc are excluded (they diffuse to the network and already pay k2_disl_v). Blank = v_mobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sweep capture width override</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>void_net_w_c</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Blank = the cavity own diameter d_cav(m) (bare geometric cross-section), which is the physical default; an explicit value overrides it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
